--- a/data/gold/results/scenarios/zorg_en_welzijn/table_1.xlsx
+++ b/data/gold/results/scenarios/zorg_en_welzijn/table_1.xlsx
@@ -415,19 +415,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>5324.893269721346</v>
+        <v>5282.353787088248</v>
       </c>
       <c r="C2">
-        <v>6047.036127486736</v>
+        <v>4813.127714787854</v>
       </c>
       <c r="D2">
-        <v>46.95906428336476</v>
+        <v>106.1413905251322</v>
       </c>
       <c r="E2">
-        <v>4234.47235581968</v>
+        <v>5581.413491720555</v>
       </c>
       <c r="F2">
-        <v>1604.461895659503</v>
+        <v>288.6032743741226</v>
       </c>
       <c r="G2">
         <v>49709.03368460669</v>
@@ -438,19 +438,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>2433.247819447399</v>
+        <v>3032.426196552249</v>
       </c>
       <c r="C3">
-        <v>2313.794041709011</v>
+        <v>2826.09787900344</v>
       </c>
       <c r="D3">
-        <v>20.1744650800205</v>
+        <v>54.4018137949363</v>
       </c>
       <c r="E3">
-        <v>2054.928206340567</v>
+        <v>3717.095917289977</v>
       </c>
       <c r="F3">
-        <v>673.2654020642273</v>
+        <v>192.2191775132592</v>
       </c>
       <c r="G3">
         <v>46664.34095919135</v>
@@ -461,19 +461,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1339.915588010944</v>
+        <v>1441.375185837561</v>
       </c>
       <c r="C4">
-        <v>2924.042064732495</v>
+        <v>1828.602963157943</v>
       </c>
       <c r="D4">
-        <v>20.05719459529767</v>
+        <v>49.50356888410434</v>
       </c>
       <c r="E4">
-        <v>1646.700904396185</v>
+        <v>1758.883308686225</v>
       </c>
       <c r="F4">
-        <v>700.9609017771467</v>
+        <v>90.18586013200851</v>
       </c>
       <c r="G4">
         <v>1950.307677832142</v>
@@ -484,19 +484,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>921.1918622629997</v>
+        <v>157.1359851774778</v>
       </c>
       <c r="C5">
-        <v>781.6681210452316</v>
+        <v>130.8949726264793</v>
       </c>
       <c r="D5">
-        <v>6.536304608046691</v>
+        <v>2.044907846091662</v>
       </c>
       <c r="E5">
-        <v>531.0508450829358</v>
+        <v>103.6418657443282</v>
       </c>
       <c r="F5">
-        <v>230.2355918181278</v>
+        <v>6.198236728855719</v>
       </c>
       <c r="G5">
         <v>1094.385047583204</v>
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>12.7</v>
+        <v>12.5221119865</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>606.2380000000001</v>
+        <v>627.294307534464</v>
       </c>
       <c r="C8">
         <v>27.5319</v>

--- a/data/gold/results/scenarios/zorg_en_welzijn/table_1.xlsx
+++ b/data/gold/results/scenarios/zorg_en_welzijn/table_1.xlsx
@@ -418,13 +418,13 @@
         <v>5282.353787088248</v>
       </c>
       <c r="C2">
-        <v>4813.127714787854</v>
+        <v>4811.230914787854</v>
       </c>
       <c r="D2">
-        <v>106.1413905251322</v>
+        <v>106.1278905251322</v>
       </c>
       <c r="E2">
-        <v>5581.413491720555</v>
+        <v>5581.290291720555</v>
       </c>
       <c r="F2">
         <v>288.6032743741226</v>
@@ -556,13 +556,13 @@
         <v>627.294307534464</v>
       </c>
       <c r="C8">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D8">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E8">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F8">
         <v>0</v>
